--- a/data/credit_bond_all_2026-09-03.xlsx
+++ b/data/credit_bond_all_2026-09-03.xlsx
@@ -1610,7 +1610,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26乐山商业银行二级01</t>
+          <t>26乐山商业银行二级资本债01</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.66</v>
+        <v>2.2667</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
@@ -5295,8 +5295,12 @@
           <t>1.60 ~ 2.30</t>
         </is>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="H23" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>77.22</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -5352,8 +5356,12 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
+      <c r="U23" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.65</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
           <t>7-</t>
@@ -5529,8 +5537,12 @@
           <t>1.70 ~ 2.10</t>
         </is>
       </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="H24" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>55.22</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>1.87</t>
@@ -5586,7 +5598,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U24" s="3"/>
+      <c r="U24" s="4" t="n">
+        <v>4.02</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -12901,7 +12915,7 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM55" s="3" t="inlineStr">
@@ -12974,7 +12988,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26成都农商行二级资本债01</t>
+          <t>26佛山金投MTN002(科创债)</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -12984,64 +12998,64 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>232680035.IB</t>
+          <t>102683535.IB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>100.0</v>
+        <v>6.0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>100.0</v>
+        <v>6.0</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>22.02</v>
+        <v>40.47</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>25成都农商行二级资本债01</t>
+          <t>26佛山金投MTN001</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>4.25Y+5.00Y</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.8578</t>
+          <t>1.7218</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>1.8500/1.8400</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>成都农村商业银行股份有限公司</t>
+          <t>佛山市金融投资控股有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>A 71.62</t>
+          <t>C- 24.61</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13061,50 +13075,50 @@
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z56" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于充实发行人二级资本</t>
+          <t>本期中期票据的发行规模为不超过6亿元,拟用于佛山市新动能产业投资基金合伙企业(有限合伙)基金以及佛山市佛控汇创股权投资合伙企业(有限合伙)的新增出资。</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中国光大银行股份有限公司,中国工商银行股份有限公司,申万宏源证券有限公司,恒丰银行股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,长城证券股份有限公司,华夏银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF56" s="3" t="inlineStr">
@@ -13119,7 +13133,7 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>成都农村商业银行股份有限公司2026年二级资本债券(第一期)</t>
+          <t>佛山市金融投资控股有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -13129,64 +13143,60 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2036-09-07</t>
-        </is>
-      </c>
-      <c r="AK56" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-04</t>
+        </is>
+      </c>
+      <c r="AK56" s="3"/>
       <c r="AL56" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM56" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO56" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ56" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR56" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS56" s="3" t="inlineStr">
-        <is>
-          <t>农商行</t>
-        </is>
-      </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
       <c r="AV56" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -13194,12 +13204,12 @@
       </c>
       <c r="AW56" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX56" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY56" s="3" t="inlineStr">
@@ -13207,12 +13217,14 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ56" s="3"/>
+      <c r="AZ56" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26佛山金投MTN002(科创债)</t>
+          <t>26安吉城运MTN001</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -13222,64 +13234,64 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>102683535.IB</t>
+          <t>102683528.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>6.0</v>
+        <v>7.5</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>6.0</v>
+        <v>7.5</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>40.47</v>
+        <v>55.61</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26佛山金投MTN001</t>
+          <t>24安吉城运MTN001</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.7218</t>
+          <t>1.7826</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>1.8000/1.7500</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>佛山市金融投资控股有限公司</t>
+          <t>浙江安吉城市运营管理集团有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 24.61</t>
+          <t>C 27.80</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13289,7 +13301,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>09-03 09:00</t>
+          <t>09-03 15:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -13303,19 +13315,19 @@
         </is>
       </c>
       <c r="U57" s="4" t="n">
-        <v>6.43</v>
+        <v>3.77</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -13326,17 +13338,17 @@
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据的发行规模为不超过6亿元,拟用于佛山市新动能产业投资基金合伙企业(有限合伙)基金以及佛山市佛控汇创股权投资合伙企业(有限合伙)的新增出资。</t>
+          <t>发行人本期中期票据发行金额为7.50亿元，用于偿还发行人即将到期的债务融资工具本金。【23 安吉城运MTN001】</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
@@ -13357,7 +13369,7 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>佛山市金融投资控股有限公司2026年度第二期科技创新债券</t>
+          <t>浙江安吉城市运营管理集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13367,7 +13379,7 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
@@ -13378,7 +13390,7 @@
       </c>
       <c r="AM57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN57" s="3" t="inlineStr">
@@ -13388,32 +13400,32 @@
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
@@ -13441,14 +13453,12 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ57" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ57" s="3"/>
     </row>
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26安吉城运MTN001</t>
+          <t>26淮北建投MTN002</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13458,64 +13468,64 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>102683528.IB</t>
+          <t>102683527.IB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>55.61</v>
+        <v>53.47</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>24安吉城运MTN001</t>
+          <t>26淮北建投MTN001</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.7826</t>
+          <t>1.7752</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.7500</t>
+          <t>1.7900/--</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>浙江安吉城市运营管理集团有限公司</t>
+          <t>淮北市建投控股集团有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>C 27.80</t>
+          <t>B- 36.95</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13525,7 +13535,7 @@
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>09-03 15:00</t>
+          <t>09-03 10:00</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
@@ -13539,19 +13549,19 @@
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>3.77</v>
+        <v>5.91</v>
       </c>
       <c r="V58" s="4" t="n">
-        <v>1.5</v>
+        <v>2.43</v>
       </c>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
@@ -13562,17 +13572,17 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>安徽省-淮北市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为7.50亿元，用于偿还发行人即将到期的债务融资工具本金。【23 安吉城运MTN001】</t>
+          <t>一、募集资金的使用发行人本次中期票据注册32.88亿元，本期发行金额为2.1亿元，拟全部用于归还发行人到期的债务融资工具。[23淮北建投MTN011]</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,杭州银行股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
@@ -13593,7 +13603,7 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>浙江安吉城市运营管理集团有限公司2026年度第一期中期票据</t>
+          <t>淮北市建投控股集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13603,7 +13613,7 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -13624,12 +13634,12 @@
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
@@ -13682,7 +13692,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26淮北建投MTN002</t>
+          <t>26闽高速MTN004</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13692,7 +13702,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>102683527.IB</t>
+          <t>102683534.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -13701,55 +13711,55 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2.1</v>
+        <v>4.0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2.1</v>
+        <v>4.0</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>53.47</v>
+        <v>35.47</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26淮北建投MTN001</t>
+          <t>26闽高速MTN003</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>2.93Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.7752</t>
+          <t>1.6989</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>1.7900/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>淮北市建投控股集团有限公司</t>
+          <t>福建省高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>B- 36.95</t>
+          <t>C- 23.10</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13759,7 +13769,7 @@
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>09-03 10:00</t>
+          <t>09-03 09:00</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -13773,40 +13783,40 @@
         </is>
       </c>
       <c r="U59" s="4" t="n">
-        <v>5.91</v>
+        <v>3.975</v>
       </c>
       <c r="V59" s="4" t="n">
-        <v>2.43</v>
+        <v>1.075</v>
       </c>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>安徽省-淮北市</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>一、募集资金的使用发行人本次中期票据注册32.88亿元，本期发行金额为2.1亿元，拟全部用于归还发行人到期的债务融资工具。[23淮北建投MTN011]</t>
+          <t>发行人本期中期票据发行规模为人民币4亿元，用于偿还发行人到期债务</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
@@ -13827,7 +13837,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>淮北市建投控股集团有限公司2026年度第二期中期票据</t>
+          <t>福建省高速公路集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13848,7 +13858,7 @@
       </c>
       <c r="AM59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN59" s="3" t="inlineStr">
@@ -13858,32 +13868,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13916,74 +13926,74 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26闽高速MTN004</t>
+          <t>26衡高02</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-03 19:00</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>102683534.IB</t>
+          <t>283889.SH</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>4.0</v>
+        <v>3.5</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>4.0</v>
+        <v>3.5</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>35.47</v>
+        <v>73.61</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26闽高速MTN003</t>
+          <t>26衡高01</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2.93Y</t>
+          <t>4.55Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.6989</t>
+          <t>2.1506</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>2.1900/2.1100</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司</t>
+          <t>衡阳高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C- 23.10</t>
+          <t>C 28.17</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -13993,7 +14003,7 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>09-03 09:00</t>
+          <t>09-03 15:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -14007,46 +14017,44 @@
         </is>
       </c>
       <c r="U60" s="4" t="n">
-        <v>3.975</v>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>1.075</v>
-      </c>
+        <v>6.34</v>
+      </c>
+      <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>2.13%~2.23%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>湖南省-衡阳市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行规模为人民币4亿元，用于偿还发行人到期债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还回售公司债券“23衡高K1”本金[23衡高K1]</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司</t>
+          <t>长江证券股份有限公司,财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
       <c r="AE60" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF60" s="3" t="inlineStr">
@@ -14056,28 +14064,28 @@
       </c>
       <c r="AG60" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司2026年度第四期中期票据</t>
+          <t>衡阳高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK60" s="3"/>
       <c r="AL60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AM60" s="3" t="inlineStr">
@@ -14097,7 +14105,7 @@
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
@@ -14107,17 +14115,17 @@
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -14150,74 +14158,74 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26衡高02</t>
+          <t>26成都农商行二级资本债01</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>09-03 19:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>283889.SH</t>
+          <t>232680035.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3.5</v>
+        <v>100.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3.5</v>
+        <v>100.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>73.61</v>
+        <v>22.02</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>26衡高01</t>
+          <t>25成都农商行二级资本债01</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>4.55Y</t>
+          <t>4.25Y+5.00Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>2.1506</t>
+          <t>1.8578</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>2.1900/2.1100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>衡阳高新控股集团有限公司</t>
+          <t>成都农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C 28.17</t>
+          <t>A 71.62</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14227,7 +14235,7 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>09-03 15:00</t>
+          <t>09-03 09:00</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -14237,48 +14245,50 @@
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U61" s="4" t="n">
-        <v>6.34</v>
-      </c>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U61" s="3"/>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>2.13%~2.23%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z61" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>湖南省-衡阳市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还回售公司债券“23衡高K1”本金[23衡高K1]</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于充实发行人二级资本</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,财信证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中国光大银行股份有限公司,中国工商银行股份有限公司,申万宏源证券有限公司,恒丰银行股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,长城证券股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AF61" s="3" t="inlineStr">
@@ -14288,73 +14298,77 @@
       </c>
       <c r="AG61" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>衡阳高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>成都农村商业银行股份有限公司2026年二级资本债券(第一期)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
-        </is>
-      </c>
-      <c r="AK61" s="3"/>
+          <t>2036-09-07</t>
+        </is>
+      </c>
+      <c r="AK61" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL61" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-07</t>
         </is>
       </c>
       <c r="AV61" s="3" t="inlineStr">
@@ -14364,12 +14378,12 @@
       </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX61" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AY61" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-03.xlsx
+++ b/data/credit_bond_all_2026-09-03.xlsx
@@ -2522,74 +2522,74 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26泰华05</t>
+          <t>26中交租赁SCP006</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>09-03 19:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>283870.SH</t>
+          <t>012682198.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2.70 ~ 3.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.93</v>
+        <v>1.44</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>125.02</v>
+        <v>18.63</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26泰华03</t>
+          <t>24交租V1</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>9.97Y</t>
+          <t>277D</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2.9605</t>
+          <t>1.5584</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>2.9700/2.8900</t>
+          <t>1.6000/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>泰州华信药业投资有限公司</t>
+          <t>中交融资租赁有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 22.48</t>
+          <t>C- 12.16</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-03 15:00</t>
+          <t>09-03 09:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2613,80 +2613,80 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.63</v>
+        <v>2.2667</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>2.86%~2.96%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过10亿元(含10亿元),扣除发行费用后,仅用于偿还到期的公司债券(23泰华06)本金。[23泰华06]</t>
+          <t>本期超短期融资券拟募集资金6亿元,拟全部用于偿还发行人即将到期的债务融资工具[26中交租赁SCP004]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,长城证券股份有限公司,平安证券股份有限公司,中泰证券股份有限公司,华金证券股份有限公司,申港证券股份有限公司</t>
+          <t>北京银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>泰州华信药业投资有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
+          <t>中交融资租赁有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2036-09-04</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN11" s="3" t="inlineStr">
@@ -2696,32 +2696,32 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26中交租赁SCP006</t>
+          <t>26安吉租赁SCP002</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2764,30 +2764,30 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>012682198.IB</t>
+          <t>012682207.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>0.68Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18.63</v>
+        <v>38.65</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -2796,32 +2796,32 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>24交租V1</t>
+          <t>26安吉租赁MTN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>277D</t>
+          <t>2.76Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.5584</t>
+          <t>1.7903</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>1.8100/1.7800</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>中交融资租赁有限公司</t>
+          <t>安吉租赁有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 12.16</t>
+          <t>C+ 32.83</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2845,22 +2845,24 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.2667</v>
-      </c>
-      <c r="V12" s="3"/>
+        <v>1.3</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.62%~1.66%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
@@ -2871,12 +2873,12 @@
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金6亿元,拟全部用于偿还发行人即将到期的债务融资工具[26中交租赁SCP004]</t>
+          <t>本期债务融资工具发行规模为5亿元,用于归还到期债务融资工具[25安吉租赁CP001]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司,江苏银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2887,7 +2889,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr">
@@ -2897,7 +2899,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>中交融资租赁有限公司2026年度第六期超短期融资券</t>
+          <t>安吉租赁有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2907,7 +2909,7 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-05-12</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2918,7 +2920,7 @@
       </c>
       <c r="AM12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN12" s="3" t="inlineStr">
@@ -2933,7 +2935,7 @@
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
@@ -2986,7 +2988,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26安吉租赁SCP002</t>
+          <t>26淮北建投MTN002</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2996,64 +2998,64 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>012682207.IB</t>
+          <t>102683527.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0.68Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.0</v>
+        <v>2.1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.0</v>
+        <v>2.1</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>38.65</v>
+        <v>53.47</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26安吉租赁MTN001</t>
+          <t>26淮北建投MTN001</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.76Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.7903</t>
+          <t>1.7752</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.8100/1.7800</t>
+          <t>1.7900/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>安吉租赁有限公司</t>
+          <t>淮北市建投控股集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.83</t>
+          <t>B- 38.00</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3063,7 +3065,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-03 09:00</t>
+          <t>09-03 10:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3077,19 +3079,19 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.3</v>
+        <v>5.9048</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.2</v>
+        <v>2.43</v>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.66%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3100,23 +3102,23 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>安徽省-淮北市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为5亿元,用于归还到期债务融资工具[25安吉租赁CP001]</t>
+          <t>一、募集资金的使用发行人本次中期票据注册32.88亿元，本期发行金额为2.1亿元，拟全部用于归还发行人到期的债务融资工具。[23淮北建投MTN011]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,江苏银行股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3131,7 +3133,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>安吉租赁有限公司2026年度第二期超短期融资券</t>
+          <t>淮北市建投控股集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3141,7 +3143,7 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2027-05-12</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
@@ -3152,7 +3154,7 @@
       </c>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
@@ -3162,32 +3164,32 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3220,7 +3222,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26淮北建投MTN002</t>
+          <t>26佛山金投MTN002(科创债)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3230,7 +3232,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683527.IB</t>
+          <t>102683535.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3239,55 +3241,55 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.1</v>
+        <v>6.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.1</v>
+        <v>6.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>53.47</v>
+        <v>40.47</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26淮北建投MTN001</t>
+          <t>26佛山金投MTN001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7752</t>
+          <t>1.7218</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.7900/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>淮北市建投控股集团有限公司</t>
+          <t>佛山市金融投资控股有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 38.00</t>
+          <t>C 29.34</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3297,7 +3299,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-03 10:00</t>
+          <t>09-03 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3311,10 +3313,10 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.9048</v>
+        <v>6.4333</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
@@ -3323,7 +3325,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3334,17 +3336,17 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>安徽省-淮北市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>一、募集资金的使用发行人本次中期票据注册32.88亿元，本期发行金额为2.1亿元，拟全部用于归还发行人到期的债务融资工具。[23淮北建投MTN011]</t>
+          <t>本期中期票据的发行规模为不超过6亿元,拟用于佛山市新动能产业投资基金合伙企业(有限合伙)基金以及佛山市佛控汇创股权投资合伙企业(有限合伙)的新增出资。</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3365,7 +3367,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>淮北市建投控股集团有限公司2026年度第二期中期票据</t>
+          <t>佛山市金融投资控股有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3386,7 +3388,7 @@
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3396,7 +3398,7 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
@@ -3406,22 +3408,22 @@
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3449,22 +3451,24 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26佛山金投MTN002(科创债)</t>
+          <t>26同煤租赁PPN001</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683535.IB</t>
+          <t>032690014.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3473,118 +3477,126 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.60 ~ 2.30</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>25赣租01</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>1.34Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>1.7881</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>1.8200/--</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>同煤漳泽(上海)融资租赁有限责任公司</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>C- 15.00</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>09-03 09:00</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V15" s="4" t="n">
         <v>1.65</v>
       </c>
-      <c r="I15" s="4" t="n">
-        <v>40.47</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>26佛山金投MTN001</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>2.61Y</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>1.7218</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>1.7400/--</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>佛山市金融投资控股有限公司</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>C 29.34</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>09-03 09:00</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>6.4333</v>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>2.29%~2.39%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z15" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据的发行规模为不超过6亿元,拟用于佛山市新动能产业投资基金合伙企业(有限合伙)基金以及佛山市佛控汇创股权投资合伙企业(有限合伙)的新增出资。</t>
+          <t>本期定向债务融资工具发行规模5亿元,用于偿还发行人有息债务。[23同租01]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3"/>
+          <t>中信银行股份有限公司,兴业银行股份有限公司,中国光大银行股份有限公司,上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>晋能控股煤业集团有限公司</t>
+        </is>
+      </c>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3599,165 +3611,163 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>佛山市金融投资控股有限公司2026年度第二期科技创新债券</t>
+          <t>同煤漳泽(上海)融资租赁有限责任公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY15" s="3" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AO15" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ15" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR15" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW15" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX15" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26同煤租赁PPN001</t>
+          <t>26首都机场SCP005</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>032690014.IB</t>
+          <t>012682204.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.30</t>
+          <t>1.29 ~ 1.49</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>77.22</v>
+        <v>12.63</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>25赣租01</t>
+          <t>24首都机场MTN001(绿色)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>1.34Y+2.00Y</t>
+          <t>199D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7881</t>
+          <t>1.4927</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.8200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>同煤漳泽(上海)融资租赁有限责任公司</t>
+          <t>首都机场集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 15.00</t>
+          <t>C- 22.81</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3767,7 +3777,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>09-03 09:00</t>
+          <t>09-03 11:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3777,58 +3787,48 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>1.65</v>
-      </c>
+        <v>1.02</v>
+      </c>
+      <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.29%~2.39%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行规模5亿元,用于偿还发行人有息债务。[23同租01]</t>
+          <t>本期发行10亿元超短期融资券，全部用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司,中国光大银行股份有限公司,上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>晋能控股煤业集团有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3843,63 +3843,63 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>同煤漳泽(上海)融资租赁有限责任公司2026年度第一期定向债务融资工具</t>
+          <t>首都机场集团有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AY16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AZ16" s="3"/>
@@ -3932,59 +3932,59 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26首都机场SCP005</t>
+          <t>26兴城Y10</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-03 19:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>012682204.IB</t>
+          <t>520458.SZ</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.29 ~ 1.49</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.38</v>
+        <v>1.98</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>12.63</v>
+        <v>58.61</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>24首都机场MTN001(绿色)</t>
+          <t>26兴城Y8</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>199D</t>
+          <t>4.82Y+N</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.4927</t>
+          <t>1.9866</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>首都机场集团有限公司</t>
+          <t>成都兴城投资集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 22.81</t>
+          <t>B- 36.68</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-03 11:00</t>
+          <t>09-03 15:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4019,21 +4019,21 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.02</v>
+        <v>3.21</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4044,23 +4044,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期发行10亿元超短期融资券，全部用于偿还发行人有息债务。</t>
+          <t>本期债券的募集资金在扣除发行费用后，将用于生产性支出</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4070,40 +4070,44 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>首都机场集团有限公司2026年度第五期超短期融资券</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AM17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -4111,27 +4115,27 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>机场</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>机场</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>机场</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4146,7 +4150,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4164,7 +4168,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26兴城Y10</t>
+          <t>26京投K3</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4174,64 +4178,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>520458.SZ</t>
+          <t>246001.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>58.61</v>
+        <v>20.61</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26兴城Y8</t>
+          <t>26京投K1</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.82Y+N</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.9866</t>
+          <t>1.7059</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/1.7025</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司</t>
+          <t>北京市基础设施投资有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 36.68</t>
+          <t>B- 36.92</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4255,17 +4259,17 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.21</v>
+        <v>3.9</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4273,20 +4277,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z18" s="3"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后，将用于生产性支出</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟用于偿还公司债务、补充流动资金及适用的法律法规允许的其他用途。</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,广发证券股份有限公司</t>
+          <t>招商证券股份有限公司,东方证券股份有限公司,中信证券股份有限公司,第一创业证券承销保荐有限责任公司,中信建投证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4302,17 +4310,17 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)(品种二)</t>
+          <t>北京市基础设施投资有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
@@ -4332,7 +4340,7 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
@@ -4342,34 +4350,34 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4382,7 +4390,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4400,7 +4408,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26京投K3</t>
+          <t>26京投K4</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4410,54 +4418,54 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>246001.SH</t>
+          <t>246002.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>15.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>20.61</v>
+        <v>30.02</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26京投K1</t>
+          <t>26京投K2</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>9.94Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7059</t>
+          <t>2.0301</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.7025</t>
+          <t>2.0400/2.0325</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -4491,7 +4499,7 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
@@ -4501,7 +4509,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4547,7 +4555,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>北京市基础设施投资有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>北京市基础设施投资有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4557,7 +4565,7 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
+          <t>2036-09-07</t>
         </is>
       </c>
       <c r="AK19" s="3" t="inlineStr">
@@ -4640,7 +4648,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26京投K4</t>
+          <t>26同辐K1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4650,64 +4658,64 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>246002.SH</t>
+          <t>246015.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>30.02</v>
+        <v>25.47</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26京投K2</t>
+          <t>24同辐K1</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>9.94Y</t>
+          <t>1.14Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2.0301</t>
+          <t>1.5472</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>2.0400/2.0325</t>
+          <t>1.5700/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>北京市基础设施投资有限公司</t>
+          <t>中国同辐股份有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 36.92</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4731,17 +4739,17 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>5.25</v>
+        <v>5.86</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4749,11 +4757,7 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>北京市</t>
@@ -4761,12 +4765,12 @@
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟用于偿还公司债务、补充流动资金及适用的法律法规允许的其他用途。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于补充公司日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。根据公司财务状况和资金使用需求,公司未来可能调整部分流动资金用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,东方证券股份有限公司,中信证券股份有限公司,第一创业证券承销保荐有限责任公司,中信建投证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4777,7 +4781,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4787,7 +4791,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>北京市基础设施投资有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种二)</t>
+          <t>中国同辐股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4797,14 +4801,10 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2036-09-07</t>
-        </is>
-      </c>
-      <c r="AK20" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-07</t>
+        </is>
+      </c>
+      <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
@@ -4822,32 +4822,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>综合医药制造</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>综合医药制造</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>医药商业</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4880,7 +4880,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26同辐K1</t>
+          <t>G26建租3</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>246015.SH</t>
+          <t>245994.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4899,89 +4899,89 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>25.47</v>
+        <v>50.47</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>26建租02</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>2.85Y</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>1.7298</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>中建投租赁股份有限公司</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>C- 17.67</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>09-03 15:00</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>24同辐K1</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>1.14Y</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>1.5472</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>1.5700/--</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>中国同辐股份有限公司</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>D 5.00</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>09-03 15:00</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>5.86</v>
+        <v>2.53</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于补充公司日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。根据公司财务状况和资金使用需求,公司未来可能调整部分流动资金用于偿还有息债务。</t>
+          <t>本期债券募集资金8.00亿元,募集资金扣除发行费用后,拟全部用于置换发行前12个月内用于绿色融资租赁项目投放的自有资金支出</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>中国同辐股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>中建投租赁股份有限公司2026年面向专业投资者公开发行绿色公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5054,32 +5054,32 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>综合医药制造</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>综合医药制造</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5112,7 +5112,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>G26建租3</t>
+          <t>26日发01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5122,64 +5122,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>245994.SH</t>
+          <t>520460.SZ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>50.47</v>
+        <v>82.61</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26建租02</t>
+          <t>25日发02</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.85Y</t>
+          <t>3.69Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.7298</t>
+          <t>2.3810</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.2800</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>中建投租赁股份有限公司</t>
+          <t>日照农发集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 17.67</t>
+          <t>C- 18.18</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5203,41 +5203,45 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.53</v>
+        <v>4.65</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省-日照市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金8.00亿元,募集资金扣除发行费用后,拟全部用于置换发行前12个月内用于绿色融资租赁项目投放的自有资金支出</t>
+          <t>本期债券募集资金3.00亿元拟用于偿还公司债券之外的有息债务。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD22" s="3"/>
+          <t>中泰证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
+        <is>
+          <t>青岛增信融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE22" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5245,88 +5249,92 @@
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>中建投租赁股份有限公司2026年面向专业投资者公开发行绿色公司债券(第三期)</t>
+          <t>日照农发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>农业综合</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
           <t>2029-09-07</t>
         </is>
       </c>
-      <c r="AK22" s="3"/>
-      <c r="AL22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO22" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ22" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR22" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX22" s="3" t="inlineStr">
@@ -5344,74 +5352,74 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26日发01</t>
+          <t>26中行TLAC非资本债02A(BC)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>09-03 19:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>520460.SZ</t>
+          <t>312610014.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3+1</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.0</v>
+        <v>150.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.0</v>
+        <v>200.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.22</v>
+        <v>1.69</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>82.61</v>
+        <v>38.59</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>25日发02</t>
+          <t>26中行TLAC非资本债01BC</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>3.69Y</t>
+          <t>2.71Y+1.00Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.3810</t>
+          <t>1.6775</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/2.2800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>日照农发集团有限公司</t>
+          <t>中国银行股份有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 18.18</t>
+          <t>S- 87.03</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5421,7 +5429,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-03 15:00</t>
+          <t>09-03 09:30</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5434,89 +5442,87 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U23" s="4" t="n">
-        <v>4.65</v>
-      </c>
+      <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z23" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>山东省-日照市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金3.00亿元拟用于偿还公司债券之外的有息债务。</t>
+          <t>本期债券募集资金在扣除发行费用后,将依据适用法律和主管部门的批准用于提升发行人总损失吸收能力。</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>青岛增信融资担保有限公司</t>
-        </is>
-      </c>
+          <t>中银国际证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,国投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,国开证券股份有限公司,广发证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,交通银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行TLAC非资本债</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>日照农发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中国银行股份有限公司2026年总损失吸收能力非资本债券(第二期)(债券通)(品种一)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
+          <t>2030-09-07</t>
         </is>
       </c>
       <c r="AK23" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN23" s="3" t="inlineStr">
@@ -5526,32 +5532,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>国有银行</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>农业综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5561,7 +5567,7 @@
       </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW23" s="3" t="inlineStr">
@@ -5571,7 +5577,7 @@
       </c>
       <c r="AX23" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY23" s="3" t="inlineStr">
@@ -5584,74 +5590,74 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26中行TLAC非资本债02A(BC)</t>
+          <t>26江苏银行债03BC</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-03 17:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>312610014.IB</t>
+          <t>212680034.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3+1</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>150.0</v>
+        <v>200.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>200.0</v>
+        <v>400.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>38.59</v>
+        <v>33.47</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26中行TLAC非资本债01BC</t>
+          <t>26江苏银行债02</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.71Y+1.00Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.6775</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5850/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>S- 87.03</t>
+          <t>A- 64.66</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5661,7 +5667,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-03 09:30</t>
+          <t>09-03 09:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5678,12 +5684,12 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5691,35 +5697,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,将依据适用法律和主管部门的批准用于提升发行人总损失吸收能力。</t>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,国投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,国开证券股份有限公司,广发证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,交通银行股份有限公司</t>
+          <t>中信证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,兴业银行股份有限公司,上海银行股份有限公司,徽商银行股份有限公司,北京银行股份有限公司,南京银行股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,东方证券股份有限公司,国开证券股份有限公司,国信证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>商业银行TLAC非资本债</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5729,7 +5731,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司2026年总损失吸收能力非资本债券(第二期)(债券通)(品种一)</t>
+          <t>江苏银行股份有限公司2026年金融债券(第三期)(债券通)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5739,14 +5741,10 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2030-09-07</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-09-07</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -5754,7 +5752,7 @@
       </c>
       <c r="AM24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN24" s="3" t="inlineStr">
@@ -5769,7 +5767,7 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
@@ -5784,7 +5782,7 @@
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>国有银行</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
@@ -5794,7 +5792,7 @@
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5804,12 +5802,12 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY24" s="3" t="inlineStr">
@@ -5822,74 +5820,74 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26江苏银行债03BC</t>
+          <t>26成都农商行二级资本债01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-03 17:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>212680034.IB</t>
+          <t>232680035.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>200.0</v>
+        <v>100.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>400.0</v>
+        <v>100.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>33.47</v>
+        <v>22.02</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26江苏银行债02</t>
+          <t>25成都农商行二级资本债01</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.25Y+5.00Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.8578</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.5850/--</t>
+          <t>1.8500/1.8400</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>成都农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>A- 64.66</t>
+          <t>B 54.76</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5916,12 +5914,12 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5929,26 +5927,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z25" s="3"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于充实发行人二级资本</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,兴业银行股份有限公司,上海银行股份有限公司,徽商银行股份有限公司,北京银行股份有限公司,南京银行股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,东方证券股份有限公司,国开证券股份有限公司,国信证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中国光大银行股份有限公司,中国工商银行股份有限公司,申万宏源证券有限公司,恒丰银行股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,长城证券股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5963,7 +5965,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司2026年金融债券(第三期)(债券通)</t>
+          <t>成都农村商业银行股份有限公司2026年二级资本债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5973,10 +5975,14 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2036-09-07</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -5984,7 +5990,7 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
@@ -5999,7 +6005,7 @@
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -6014,7 +6020,7 @@
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
@@ -6024,7 +6030,7 @@
       </c>
       <c r="AU25" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-07</t>
         </is>
       </c>
       <c r="AV25" s="3" t="inlineStr">
@@ -6034,12 +6040,12 @@
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AY25" s="3" t="inlineStr">
@@ -6052,7 +6058,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26成都农商行二级资本债01</t>
+          <t>26亚洲开发银行债02BC</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6062,64 +6068,56 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>232680035.IB</t>
+          <t>292680031.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>100.0</v>
+        <v>30.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.39 ~ 1.59</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>22.02</v>
+        <v>25.47</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>25成都农商行二级资本债01</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>4.25Y+5.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.8578</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.8500/1.8400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>成都农村商业银行股份有限公司</t>
+          <t>亚洲开发银行</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B 54.76</t>
+          <t>D+ 7.02</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6142,52 +6140,42 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U26" s="3"/>
+      <c r="U26" s="4" t="n">
+        <v>2.0433</v>
+      </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>1.85%~1.95%</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X26" s="3"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="AA26" s="3" t="inlineStr">
-        <is>
-          <t>四川省-成都市</t>
-        </is>
-      </c>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于充实发行人二级资本</t>
+          <t>亚行在本项目项下发行的本债券的募集资金净额将纳入亚行的常规资本来源,用于其普通业务运营。在本项目项下,至多100%的募集资金净额可汇出中国并兑换为美元及/或其他货币。就本期债券而言,至多100%的募集资金净额可汇出中国并兑换为美元。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中国光大银行股份有限公司,中国工商银行股份有限公司,申万宏源证券有限公司,恒丰银行股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,长城证券股份有限公司,华夏银行股份有限公司</t>
+          <t>中国银行股份有限公司,德意志银行(中国)有限公司,中信证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>国际机构债券</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -6197,7 +6185,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>成都农村商业银行股份有限公司2026年二级资本债券(第一期)</t>
+          <t>亚洲开发银行2026年度第二期人民币债券(债券通)(品种一)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6207,14 +6195,10 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2036-09-07</t>
-        </is>
-      </c>
-      <c r="AK26" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-07</t>
+        </is>
+      </c>
+      <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -6222,7 +6206,7 @@
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
@@ -6235,11 +6219,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+      <c r="AP26" s="3"/>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -6252,7 +6232,7 @@
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>其他银行</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
@@ -6262,7 +6242,7 @@
       </c>
       <c r="AU26" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AV26" s="3" t="inlineStr">
@@ -6272,12 +6252,12 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY26" s="3" t="inlineStr">
@@ -6285,155 +6265,177 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26亚洲开发银行债02BC</t>
+          <t>26济轨01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-03 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>292680031.IB</t>
+          <t>283900.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>80.0</v>
+        <v>25.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.39 ~ 1.59</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.5</v>
+        <v>2.44</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>25.47</v>
+        <v>76.02</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>25济轨06</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>8.75Y</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>2.2516</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>--/2.2700</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>济南轨道交通集团有限公司</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>C+ 32.51</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>09-03 15:00</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>亚洲开发银行</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>D+ 7.02</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>09-03 09:00</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.0433</v>
+        <v>1.95</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X27" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>2.29%~2.39%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
-      <c r="AA27" s="3"/>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>亚行在本项目项下发行的本债券的募集资金净额将纳入亚行的常规资本来源,用于其普通业务运营。在本项目项下,至多100%的募集资金净额可汇出中国并兑换为美元及/或其他货币。就本期债券而言,至多100%的募集资金净额可汇出中国并兑换为美元。</t>
+          <t>本期债券募集资金25亿元扣除发行费用后,拟用于偿还公司债券本金。[21济轨01]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,德意志银行(中国)有限公司,中信证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中泰证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>国际机构债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>亚洲开发银行2026年度第二期人民币债券(债券通)(品种一)</t>
+          <t>济南轨道交通集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2036-09-07</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6448,28 +6450,32 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP27" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他银行</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6497,14 +6503,12 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ27" s="4" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="AZ27" s="3"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26济轨01</t>
+          <t>26温公02</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6514,64 +6518,64 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>283900.SH</t>
+          <t>283850.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.44</v>
+        <v>1.71</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>76.02</v>
+        <v>31.61</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25济轨06</t>
+          <t>26温公01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>8.75Y</t>
+          <t>2.80Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2.2516</t>
+          <t>1.7657</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/2.2700</t>
+          <t>1.7500/1.7200</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>济南轨道交通集团有限公司</t>
+          <t>温州市公用事业发展集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.51</t>
+          <t>C- 17.58</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6595,17 +6599,17 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.95</v>
+        <v>6.98</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.29%~2.39%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6616,17 +6620,17 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金25亿元扣除发行费用后,拟用于偿还公司债券本金。[21济轨01]</t>
+          <t>本期债券拟募集资金规模不超过5亿元(含5亿元),扣除发行费用后拟用于偿还有息债务等监管批复的用途</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中泰证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
+          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6647,7 +6651,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>济南轨道交通集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>温州市公用事业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6657,7 +6661,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2036-09-07</t>
+          <t>2031-09-07</t>
         </is>
       </c>
       <c r="AK28" s="3" t="inlineStr">
@@ -6682,37 +6686,37 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
@@ -6722,7 +6726,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6740,7 +6744,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26温公02</t>
+          <t>26津金01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6750,64 +6754,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>283850.SH</t>
+          <t>283823.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>4.98</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.0</v>
+        <v>4.98</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>2.00 ~ 3.60</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.71</v>
+        <v>2.35</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>31.61</v>
+        <v>95.61</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26温公01</t>
+          <t>21津金01</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.80Y</t>
+          <t>82D</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7657</t>
+          <t>2.9730</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>温州市公用事业发展集团有限公司</t>
+          <t>天津市金地城市建设有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 17.58</t>
+          <t>C- 15.00</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6831,38 +6835,38 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>6.98</v>
+        <v>4.55</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>3.12%~3.22%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>天津市-宝坻区</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金规模不超过5亿元(含5亿元),扣除发行费用后拟用于偿还有息债务等监管批复的用途</t>
+          <t>本期公司债券发行规模为不超过4.98亿元(含4.98亿元),本期债券的募集资金在扣除发行费用后,全部用于偿还到期的公司债券本金[21 津金01]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司</t>
+          <t>方正证券承销保荐有限责任公司,国金证券股份有限公司,渤海证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6883,7 +6887,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>温州市公用事业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>天津市金地城市建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6918,37 +6922,37 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6958,7 +6962,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6976,7 +6980,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26津金01</t>
+          <t>26闽冶02</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6986,49 +6990,49 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283823.SH</t>
+          <t>245988.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.98</v>
+        <v>10.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.98</v>
+        <v>10.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.60</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>95.61</v>
+        <v>34.47</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>21津金01</t>
+          <t>24闽冶01</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>82D</t>
+          <t>3.02Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2.9730</t>
+          <t>1.6932</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7038,12 +7042,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>天津市金地城市建设有限公司</t>
+          <t>福建省冶金(控股)有限责任公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 15.00</t>
+          <t>C- 13.91</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7067,38 +7071,38 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.55</v>
+        <v>5.0</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>3.12%~3.22%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>天津市-宝坻区</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行规模为不超过4.98亿元(含4.98亿元),本期债券的募集资金在扣除发行费用后,全部用于偿还到期的公司债券本金[21 津金01]</t>
+          <t>本期公司债券拟发行不超过人民币10亿元(含10亿元),本期债券的募集资金扣除发行费用后将用于偿还到期公司债券25闽冶01本金[25闽冶01]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>方正证券承销保荐有限责任公司,国金证券股份有限公司,渤海证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7119,24 +7123,20 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>天津市金地城市建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>福建省冶金(控股)有限责任公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-07</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合矿产</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合矿产</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7212,59 +7212,59 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26闽冶02</t>
+          <t>26中行TLAC非资本债02B(BC)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-03 19:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>245988.SH</t>
+          <t>312610015.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+1</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.0</v>
+        <v>200.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>34.47</v>
+        <v>33.04</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24闽冶01</t>
+          <t>26中行TLAC非资本债01BC</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>3.02Y</t>
+          <t>2.71Y+1.00Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.6932</t>
+          <t>1.6775</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>福建省冶金(控股)有限责任公司</t>
+          <t>中国银行股份有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 13.91</t>
+          <t>S- 87.03</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-03 15:00</t>
+          <t>09-03 09:30</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7302,18 +7302,16 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U31" s="4" t="n">
-        <v>5.0</v>
-      </c>
+      <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7321,41 +7319,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z31" s="3"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券拟发行不超过人民币10亿元(含10亿元),本期债券的募集资金扣除发行费用后将用于偿还到期公司债券25闽冶01本金[25闽冶01]</t>
+          <t>本期债券募集资金在扣除发行费用后,将依据适用法律和主管部门的批准用于提升发行人总损失吸收能力。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,兴业证券股份有限公司</t>
+          <t>中银国际证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,国投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,国开证券股份有限公司,广发证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行TLAC非资本债</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>福建省冶金(控股)有限责任公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>中国银行股份有限公司2026年总损失吸收能力非资本债券(第二期)(债券通)(品种二)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7365,18 +7367,18 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2032-09-07</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7386,37 +7388,37 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>综合矿产</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>综合矿产</t>
+          <t>国有银行</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-07</t>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7426,12 +7428,12 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY31" s="3" t="inlineStr">
@@ -7444,59 +7446,59 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26中行TLAC非资本债02B(BC)</t>
+          <t>26泰华05</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-03 19:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>312610015.IB</t>
+          <t>283870.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5+1</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>200.0</v>
+        <v>10.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>2.70 ~ 3.50</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.79</v>
+        <v>2.93</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>33.04</v>
+        <v>125.02</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26中行TLAC非资本债01BC</t>
+          <t>26泰华03</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.71Y+1.00Y</t>
+          <t>9.97Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6775</t>
+          <t>2.9605</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7506,12 +7508,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司</t>
+          <t>泰州华信药业投资有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>S- 87.03</t>
+          <t>C- 22.48</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7521,7 +7523,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-03 09:30</t>
+          <t>09-03 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7531,126 +7533,124 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U32" s="3"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>2.63</v>
+      </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>2.86%~2.96%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,将依据适用法律和主管部门的批准用于提升发行人总损失吸收能力。</t>
+          <t>本期债券发行总额不超过10亿元(含10亿元),扣除发行费用后,仅用于偿还到期的公司债券(23泰华06)本金。[23泰华06]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,国投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,国开证券股份有限公司,广发证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,交通银行股份有限公司</t>
+          <t>广发证券股份有限公司,长城证券股份有限公司,平安证券股份有限公司,中泰证券股份有限公司,华金证券股份有限公司,申港证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>商业银行TLAC非资本债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司2026年总损失吸收能力非资本债券(第二期)(债券通)(品种二)</t>
+          <t>泰州华信药业投资有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2032-09-07</t>
+          <t>2036-09-04</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>国有银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>医药商业</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AV32" s="3" t="inlineStr">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY32" s="3" t="inlineStr">
@@ -7678,74 +7678,74 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26铁道15</t>
+          <t>26交旅04</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-03 11:00</t>
+          <t>09-03 19:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2680031.IB</t>
+          <t>283792.SH</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>50.0</v>
+        <v>7.35</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>50.0</v>
+        <v>7.35</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.08 ~ 2.08</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.02</v>
+        <v>66.61</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26铁道13</t>
+          <t>26交旅03</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>9.96Y</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.8211</t>
+          <t>2.0067</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/1.8100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>中国国家铁路集团有限公司</t>
+          <t>新沂市交通文旅集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 15.93</t>
+          <t>C 29.24</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-03 10:00</t>
+          <t>09-03 15:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7769,86 +7769,80 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.214</v>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>2.75</v>
-      </c>
+        <v>2.3469</v>
+      </c>
+      <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>2.13%~2.23%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>中华人民共和国</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>经证监会同意，本期债券发行募集资金 100 亿元，全部用于债务结构调整。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还到期的公司债券[23文旅01,G20新交1,23文旅02]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国开证券股份有限公司,华泰联合证券有限责任公司,中银国际证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3" t="inlineStr">
-        <is>
-          <t>铁路建设基金</t>
-        </is>
-      </c>
+          <t>国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>政府支持债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>2026年第十一期中国铁路建设债券(10年期)</t>
+          <t>新沂市交通文旅集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2036-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
@@ -7858,32 +7852,32 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7893,7 +7887,7 @@
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
@@ -7916,74 +7910,74 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26川华西SCP003</t>
+          <t>26铁道15</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-03 11:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>012682205.IB</t>
+          <t>2680031.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.77</t>
+          <t>1.08 ~ 2.08</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>51.65</v>
+        <v>9.02</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>24川华西MTN001</t>
+          <t>26铁道13</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>206D</t>
+          <t>9.96Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.7745</t>
+          <t>1.8211</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8100</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>四川华西集团有限公司</t>
+          <t>中国国家铁路集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.89</t>
+          <t>C- 15.93</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7993,7 +7987,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-03 11:00</t>
+          <t>09-03 10:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8007,51 +8001,55 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.5</v>
+        <v>2.214</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>12.5</v>
+        <v>2.75</v>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t>1.75%~1.79%</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X34" s="3"/>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z34" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>中华人民共和国</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券计划发行规模为5.00亿元,募集资金扣除承销费后,拟用于偿还发行人到期债务融资工具。[25川华西SCP006]</t>
+          <t>经证监会同意，本期债券发行募集资金 100 亿元，全部用于债务结构调整。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3"/>
+          <t>中信证券股份有限公司,国开证券股份有限公司,华泰联合证券有限责任公司,中银国际证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr">
+        <is>
+          <t>铁路建设基金</t>
+        </is>
+      </c>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>政府支持债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
@@ -8061,7 +8059,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>四川华西集团有限公司2026年度第三期超短期融资券</t>
+          <t>2026年第十一期中国铁路建设债券(10年期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8071,13 +8069,13 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2027-06-01</t>
+          <t>2036-09-04</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8097,27 +8095,27 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8127,7 +8125,7 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -8150,7 +8148,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26金源华兴PPN001</t>
+          <t>26川华西SCP003</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8160,12 +8158,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>032680515.IB</t>
+          <t>012682205.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -8176,33 +8174,33 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>1.50 ~ 1.77</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>91.59</v>
+        <v>51.65</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26金源华兴MTN002</t>
+          <t>24川华西MTN001</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>1.68Y+1.00Y</t>
+          <t>206D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2.1967</t>
+          <t>1.7745</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -8212,12 +8210,12 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>金源华兴融资租赁有限公司</t>
+          <t>四川华西集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.04</t>
+          <t>C+ 34.89</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8227,7 +8225,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-03 15:00</t>
+          <t>09-03 11:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8241,19 +8239,19 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>1.0</v>
+        <v>12.5</v>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>2.47%~2.57%</t>
+          <t>1.75%~1.79%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8264,23 +8262,23 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江西省-上饶市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为人民币0亿元，发行金额上限为人民币5亿元，扣除发行费用后拟全部用于偿还有息债务</t>
+          <t>本期债券计划发行规模为5.00亿元,募集资金扣除承销费后,拟用于偿还发行人到期债务融资工具。[25川华西SCP006]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,江西银行股份有限公司,中信银行股份有限公司,九江银行股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -8295,17 +8293,17 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>金源华兴融资租赁有限公司2026年度第一期定向债务融资工具</t>
+          <t>四川华西集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2030-09-04</t>
+          <t>2027-06-01</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
@@ -8326,37 +8324,37 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
@@ -8366,7 +8364,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8384,7 +8382,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26南通沿海PPN004</t>
+          <t>26金源华兴PPN001</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8394,64 +8392,64 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>032690015.IB</t>
+          <t>032680515.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>48.47</v>
+        <v>91.59</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26南通沿海PPN003</t>
+          <t>26金源华兴MTN002</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>1.68Y+1.00Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7628</t>
+          <t>2.1967</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.7800/1.7200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>南通沿海开发集团有限公司</t>
+          <t>金源华兴融资租赁有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 42.22</t>
+          <t>D+ 7.04</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8461,7 +8459,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-03 09:00</t>
+          <t>09-03 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8475,40 +8473,40 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>4.63</v>
+        <v>1.74</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>1.02</v>
+        <v>1.0</v>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>2.47%~2.57%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>江西省-上饶市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为10.00亿元,募集资金用于偿还发行人本部的债务融资工具本金[26南通沿海SCP005]</t>
+          <t>本期债务融资工具基础发行金额为人民币0亿元，发行金额上限为人民币5亿元，扣除发行费用后拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,江西银行股份有限公司,中信银行股份有限公司,九江银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8529,7 +8527,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>南通沿海开发集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>金源华兴融资租赁有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8539,7 +8537,7 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2030-09-04</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
@@ -8560,37 +8558,37 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>其他休闲服务</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AV36" s="3" t="inlineStr">
@@ -8600,7 +8598,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8613,14 +8611,12 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ36" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ36" s="3"/>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26日照新融PPN001</t>
+          <t>26南通沿海PPN004</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8630,64 +8626,64 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>032680514.IB</t>
+          <t>032690015.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.50</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>110.61</v>
+        <v>48.47</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25新融01</t>
+          <t>26南通沿海PPN003</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>3.71Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2.3671</t>
+          <t>1.7628</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/1.7200</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>日照新融产业投资发展有限公司</t>
+          <t>南通沿海开发集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B- 38.33</t>
+          <t>B- 42.22</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8711,51 +8707,43 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>5.56</v>
+        <v>4.63</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>3.52</v>
+        <v>1.02</v>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>2.36%~2.46%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>山东省-日照市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具拟采用动态调整方式发行，基础发行规模0亿元，发行规模上限5亿元，募集资金用于偿还有息债务。</t>
+          <t>发行人本期定向债务融资工具发行金额为10.00亿元,募集资金用于偿还发行人本部的债务融资工具本金[26南通沿海SCP005]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>青岛银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD37" s="3" t="inlineStr">
-        <is>
-          <t>日照高新发展集团有限公司</t>
-        </is>
-      </c>
+          <t>江苏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
           <t>定向工具(PPN)</t>
@@ -8773,7 +8761,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>日照新融产业投资发展有限公司2026年度第一期定向债务融资工具</t>
+          <t>南通沿海开发集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8783,7 +8771,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8804,12 +8792,12 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
@@ -8819,17 +8807,17 @@
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>其他休闲服务</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8839,7 +8827,7 @@
       </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW37" s="3" t="inlineStr">
@@ -8857,12 +8845,14 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26悦达PPN002</t>
+          <t>26日照新融PPN001</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8872,7 +8862,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>032680516.IB</t>
+          <t>032680514.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -8888,33 +8878,33 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>2.50 ~ 3.50</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>84.61</v>
+        <v>110.61</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26悦达PPN001</t>
+          <t>25新融01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>4.76Y</t>
+          <t>3.71Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2.3657</t>
+          <t>2.3671</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8924,12 +8914,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>江苏悦达集团有限公司</t>
+          <t>日照新融产业投资发展有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C 29.73</t>
+          <t>B- 38.33</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8953,43 +8943,51 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>3.48</v>
+        <v>5.56</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>1.0</v>
+        <v>3.52</v>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>2.48%~2.58%</t>
+          <t>2.36%~2.46%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z38" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>山东省-日照市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行规模为5亿元，拟全部用于偿还公司有息债务本息[24悦达MTN004]</t>
+          <t>本期定向债务融资工具拟采用动态调整方式发行，基础发行规模0亿元，发行规模上限5亿元，募集资金用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,南京银行股份有限公司,兴业银行股份有限公司,申万宏源证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3"/>
+          <t>青岛银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>日照高新发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE38" s="3" t="inlineStr">
         <is>
           <t>定向工具(PPN)</t>
@@ -9007,7 +9005,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>江苏悦达集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>日照新融产业投资发展有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -9038,32 +9036,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9073,7 +9071,7 @@
       </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -9091,14 +9089,12 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ38" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ38" s="3"/>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26南航股SCP017</t>
+          <t>26悦达PPN002</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9108,64 +9104,64 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>012682081.IB</t>
+          <t>032680516.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0.65Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.38</v>
+        <v>2.24</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>19.65</v>
+        <v>84.61</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26南航股SCP018</t>
+          <t>26悦达PPN001</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>231D</t>
+          <t>4.76Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.5113</t>
+          <t>2.3657</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.5300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>中国南方航空股份有限公司</t>
+          <t>江苏悦达集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B 53.10</t>
+          <t>C 29.73</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9189,19 +9185,19 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>2.83</v>
+        <v>3.48</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>2.48%~2.58%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9212,28 +9208,28 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额为10亿元，发行人计划将用于偿还存量有息债务。</t>
+          <t>本期定向债务融资工具发行规模为5亿元，拟全部用于偿还公司有息债务本息[24悦达MTN004]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,南京银行股份有限公司,兴业银行股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
@@ -9243,17 +9239,17 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>中国南方航空股份有限公司2026年度第十七期超短期融资券</t>
+          <t>江苏悦达集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
@@ -9279,27 +9275,27 @@
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9327,113 +9323,117 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ39" s="3"/>
+      <c r="AZ39" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26兴城Y9</t>
+          <t>26南航股SCP017</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>09-03 19:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>520457.SZ</t>
+          <t>012682081.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.65Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F40" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>26南航股SCP018</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>231D</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>1.5113</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>1.5300/--</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>中国南方航空股份有限公司</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>B 53.10</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>09-03 09:00</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V40" s="4" t="n">
         <v>2.0</v>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>53.47</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>26兴城Y7</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>2.82Y+N</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>1.7630</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>成都兴城投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t>B- 36.68</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t>09-03 15:00</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9444,101 +9444,101 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后，将用于生产性支出，具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途，具体用途根据发行人资金需求情况确定。</t>
+          <t>本期债务融资工具发行金额为10亿元，发行人计划将用于偿还存量有息债务。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,广发证券股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)(品种一)</t>
+          <t>中国南方航空股份有限公司2026年度第十七期超短期融资券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2027-04-30</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>航空运输</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO40" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ40" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR40" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS40" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV40" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9564,7 +9564,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26泰华04(取消发行)</t>
+          <t>26兴城Y9</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9574,43 +9574,49 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>DY283869.SH</t>
+          <t>520457.SZ</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>53.47</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26泰华01</t>
+          <t>26兴城Y7</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.56Y</t>
+          <t>2.82Y+N</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2.0673</t>
+          <t>1.7630</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -9620,12 +9626,12 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>泰州华信药业投资有限公司</t>
+          <t>成都兴城投资集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 22.48</t>
+          <t>B- 36.68</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9645,40 +9651,42 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U41" s="3"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>6.25</v>
+      </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>2.26%~2.36%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过10亿元(含10亿元),扣除发行费用后,仅用于偿还到期的公司债券(23泰华06)本金。[23泰华06]</t>
+          <t>本期债券的募集资金在扣除发行费用后，将用于生产性支出，具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途，具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,长城证券股份有限公司,平安证券股份有限公司,中泰证券股份有限公司,华金证券股份有限公司,申港证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9694,12 +9702,12 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>泰州华信药业投资有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种一)(取消发行)</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9709,7 +9717,7 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9725,37 +9733,37 @@
       </c>
       <c r="AN41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9770,7 +9778,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9788,7 +9796,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26桂债03</t>
+          <t>26泰华04(取消发行)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9798,64 +9806,58 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>520453.SZ</t>
+          <t>DY283869.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>7.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>87.47</v>
-      </c>
+          <t>1.70 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26桂债02</t>
+          <t>26泰华01</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>4.56Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.1434</t>
+          <t>2.0673</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/2.0000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司</t>
+          <t>泰州华信药业投资有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B- 35.64</t>
+          <t>C- 22.48</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9875,42 +9877,40 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="n">
-        <v>3.16</v>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>2.26%~2.36%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还有息债务</t>
+          <t>本期债券发行总额不超过10亿元(含10亿元),扣除发行费用后,仅用于偿还到期的公司债券(23泰华06)本金。[23泰华06]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中国银河证券股份有限公司,国海证券股份有限公司,中信建投证券股份有限公司,华创证券有限责任公司</t>
+          <t>广发证券股份有限公司,长城证券股份有限公司,平安证券股份有限公司,中泰证券股份有限公司,华金证券股份有限公司,申港证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
@@ -9926,12 +9926,12 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>泰州华信药业投资有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
@@ -9952,42 +9952,42 @@
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>医药商业</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -10020,7 +10020,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26交旅04</t>
+          <t>26桂债03</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10030,64 +10030,64 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283792.SH</t>
+          <t>520453.SZ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>7.35</v>
+        <v>7.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>7.35</v>
+        <v>7.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>66.61</v>
+        <v>87.47</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26交旅03</t>
+          <t>26桂债02</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2.0067</t>
+          <t>2.1434</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0000</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>新沂市交通文旅集团有限公司</t>
+          <t>广西金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C 29.24</t>
+          <t>B- 35.64</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10107,11 +10107,11 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>2.3469</v>
+        <v>3.16</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
@@ -10121,28 +10121,28 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>2.13%~2.23%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还到期的公司债券[23文旅01,G20新交1,23文旅02]</t>
+          <t>本期债券募集资金拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司</t>
+          <t>广发证券股份有限公司,中国银河证券股份有限公司,国海证券股份有限公司,中信建投证券股份有限公司,华创证券有限责任公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
@@ -10158,12 +10158,12 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>新沂市交通文旅集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -10173,13 +10173,13 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -10189,32 +10189,32 @@
       </c>
       <c r="AN43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
